--- a/docs/competitive-analysis.xlsx
+++ b/docs/competitive-analysis.xlsx
@@ -14,6 +14,7 @@
     <sheet name="xtraCHEF Deep Dive" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Pricing" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Toast → v2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Software Landscape" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,6 +75,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="000E1B17"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="000E1B17"/>
       <sz val="11"/>
     </font>
@@ -131,7 +138,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -153,11 +160,55 @@
         <color rgb="00DDDDDD"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -224,6 +275,28 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4875,4 +4948,1891 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Restaurant software landscape — what's out there, what Mise should do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>13 categories · leading vendors · core features · verdict for Mise. Source: 2025-26 restaurant tech surveys, vendor sites, G2/Capterra reviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Sub-feature</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>What it does</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Who leads</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Verdict for Mise</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>POS — Point of Sale</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="7" t="inlineStr"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Order entry + payments</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Take orders, fire to kitchen, accept card/cash/Apple Pay, split bills, comp/void with reason.</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Toast, Square for Restaurants, Lightspeed, TouchBistro, Clover</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>We integrate with Toast for sales feed. Building a POS is a 3-year detour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="9" t="inlineStr"/>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Tableside handheld</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Servers take orders on a phone/handheld at the table; tickets fire instantly.</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Toast Go, Square Handheld, Lightspeed Order Anywhere</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Same logic. Toast handhelds are entrenched at Daniel's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="7" t="inlineStr"/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Offline mode</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>POS keeps taking orders when internet drops; syncs on reconnect.</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Toast (partial), Square, TouchBistro</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>Have</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Our PWA offline pattern is more aggressive than most POSes. Carry that to inventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="9" t="inlineStr"/>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Multi-location menu sync</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Push menu changes across multiple locations from one console.</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Toast, Lightspeed, Square multi-unit</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Not our wedge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Inventory &amp; Back-Office</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="26" t="n"/>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="9" t="inlineStr"/>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Cycle counts (mobile)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Counter walks station, taps quantities, submits.</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Mise, MarketMan, MarginEdge, xtraCHEF (Pro), R365</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>Have</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Our core. Counter-first UX is the differentiator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="7" t="inlineStr"/>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Invoice OCR / AP automation</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Photograph vendor invoice, extract line items + prices, route for approval.</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>MarginEdge (lead), xtraCHEF, R365</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>v2 candidate</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Google Document AI integration. P0 for AvT to work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="9" t="inlineStr"/>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Recipe BOM + costing</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Map menu dishes to inventory items + yields, roll up theoretical food cost.</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>MarketMan, R365, Apicbase, xtraCHEF Pro</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>v2 candidate</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Scaffold in place. Builder UI is the 8–12 wk piece.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="7" t="inlineStr"/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Actual vs Theoretical (AvT)</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Sales × recipes = theoretical usage; minus actual count = waste/theft/shrink.</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>R365 (lead), MarginEdge, xtraCHEF Pro, MarketMan</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>v2 candidate</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Placeholder shipped. Real numbers gated on POS + recipes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="9" t="inlineStr"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Below-par alerts / reorder suggestions</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Notify when last count falls below par; suggest order quantity.</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>MarketMan, MarginEdge, R365, xtraCHEF Pro</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>Have</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Live today. Notifier delivery (email/Slack) is the v2 piece.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="7" t="inlineStr"/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Vendor / PO management</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Track vendors, create POs, receive against PO, three-way match.</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>MarketMan, R365 (core), Apicbase</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>v3 candidate</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Big surface. CSV export bridges the gap for years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="9" t="inlineStr"/>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Barcode + scale scanning</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Scan barcode to count; Bluetooth scale for bottle weights.</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>WISK (bar), MarginEdge Freepour, R365</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>Skip — out of scope</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Fine-dining inventory is rarely barcoded. D's bar SKUs maybe later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>Scheduling &amp; Labor</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="9" t="inlineStr"/>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Shift scheduling</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Drag-drop weekly schedule, role/station, employee preferences.</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>7shifts (lead), HotSchedules, When I Work, Homebase, Sling, Deputy</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Mature category. 7shifts is the obvious integration target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="7" t="inlineStr"/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Labor forecast vs sales</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Predict optimal staffing from forecast sales + historical labor %.</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>7shifts, HotSchedules, Restaurant365</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Adjacent to AvT but a different math problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="9" t="inlineStr"/>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Time clock + geofence</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Punch in/out, prevent buddy-punching, GPS verification.</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>7shifts, Homebase, Toast Payroll</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Not our scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="7" t="inlineStr"/>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Tip pooling + tip-out</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Calculate tip splits across roles, post to payroll.</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>7shifts, Toast Payroll, TipHaus</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>High-compliance category; partner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="9" t="inlineStr"/>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Compliance flags (NYC fast food, predictive scheduling)</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Warn before publishing a schedule that violates local labor law.</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>7shifts, HotSchedules</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Jurisdictional table-stakes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>Reservations &amp; Guest</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="n"/>
+      <c r="C24" s="26" t="n"/>
+      <c r="D24" s="26" t="n"/>
+      <c r="E24" s="26" t="n"/>
+      <c r="F24" s="26" t="n"/>
+    </row>
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="9" t="inlineStr"/>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Online booking + waitlist</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Guest books online; SMS notifications; walk-in waitlist.</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>OpenTable, Resy, SevenRooms, Tock, Yelp Reservations</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Daniel's FTL is on Resy. Don't disturb the lobby.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="44" customHeight="1">
+      <c r="A26" s="7" t="inlineStr"/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Guest CRM (preferences, allergies, visit history)</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>360° guest profile across all visits; staff see notes at the door.</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>SevenRooms (lead), Tock, OpenTable GuestCenter</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>SevenRooms is the fine-dining default. Integrate if anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="44" customHeight="1">
+      <c r="A27" s="9" t="inlineStr"/>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Prepaid tickets / deposits</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Charge deposit at booking; ticketed tasting menus.</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Tock (lead), Resy (post-merger)</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Tasting-menu specialty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44" customHeight="1">
+      <c r="A28" s="7" t="inlineStr"/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Table management (live floor)</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Visual floor map; assign tables; turn times.</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>SevenRooms, Resy, OpenTable, Tock</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Hostess-facing tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Online Ordering &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+      <c r="E29" s="26" t="n"/>
+      <c r="F29" s="26" t="n"/>
+    </row>
+    <row r="30" ht="44" customHeight="1">
+      <c r="A30" s="7" t="inlineStr"/>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Direct ordering (own website)</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Branded ordering page on your domain; no commission.</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>ChowNow, Olo, Toast Online Order, Square Online</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Daniel's doesn't currently do delivery. D's Sports does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="44" customHeight="1">
+      <c r="A31" s="9" t="inlineStr"/>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Marketplace listings (DoorDash, Uber Eats, Grubhub)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Be discoverable on third-party apps; pay 15–30% commission.</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>DoorDash, Uber Eats, Grubhub</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Aggregator economics; not software we own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="1">
+      <c r="A32" s="7" t="inlineStr"/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Order aggregation (one dashboard)</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Consolidate orders from all 3rd-party apps into one POS feed.</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Olo Rails, Otter, Cuboh, Chowly, Deliverect</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Mature space.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Loyalty</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+      <c r="E33" s="26" t="n"/>
+      <c r="F33" s="26" t="n"/>
+    </row>
+    <row r="34" ht="44" customHeight="1">
+      <c r="A34" s="7" t="inlineStr"/>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Email + SMS campaigns</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Send promo emails / texts based on guest segments.</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Punchh, Toast Marketing, Yotpo, Mailchimp</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Commodity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="44" customHeight="1">
+      <c r="A35" s="9" t="inlineStr"/>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Loyalty / points / tiers</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Earn points per visit; redeem for rewards; tiered status.</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Punchh (enterprise), Square Loyalty, Toast Loyalty, Marsello</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Per-restaurant loyalty makes more sense for D's than Daniel's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="7" t="inlineStr"/>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Guest data platform (CDP)</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Unify guest data from POS + online + delivery + WiFi.</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Bikky (lead), Punchh, SevenRooms (partial)</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Heavy. Years of work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="9" t="inlineStr"/>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Reviews / reputation</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Aggregate Yelp + Google + TripAdvisor reviews; respond from one inbox.</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Reputation.com, Yelp for Business, Toast Reputation</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Adjacent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Accounting &amp; Finance</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+      <c r="E38" s="26" t="n"/>
+      <c r="F38" s="26" t="n"/>
+    </row>
+    <row r="39" ht="44" customHeight="1">
+      <c r="A39" s="9" t="inlineStr"/>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Daily sales journal</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Pull yesterday's POS sales, deposits, voids, comps into GL.</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>R365 (lead), MarginEdge, QuickBooks + Shogo</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>R365's strongest module. Wire to Toast directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="44" customHeight="1">
+      <c r="A40" s="7" t="inlineStr"/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Accounts payable (invoice → approval → pay)</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Vendor bill workflow with approval chain.</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>R365, MarginEdge, Bill.com</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Office staff workflow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="44" customHeight="1">
+      <c r="A41" s="9" t="inlineStr"/>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>GL + financial reporting</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Standard ledger, P&amp;L, balance sheet.</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>R365, QuickBooks, Sage Intacct, NetSuite</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>Accounting team's tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="44" customHeight="1">
+      <c r="A42" s="7" t="inlineStr"/>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Multi-entity / intercompany</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Consolidate across multiple restaurant LLCs.</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>R365, Sage Intacct (10+ locations)</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>Gioia's accountant problem, not ours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="n"/>
+      <c r="C43" s="26" t="n"/>
+      <c r="D43" s="26" t="n"/>
+      <c r="E43" s="26" t="n"/>
+      <c r="F43" s="26" t="n"/>
+    </row>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="7" t="inlineStr"/>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Sales by item / menu mix</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Which dishes sold; movers / draggers.</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Toast Reporting, R365, Square Analytics</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Skip — POS owns it</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>We don't store sales. Toast does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="44" customHeight="1">
+      <c r="A45" s="9" t="inlineStr"/>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Prime cost dashboard (labor + food / sales)</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>The top KPI for restaurant ops.</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>R365 (lead), 7shifts, MarginEdge</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>v3 candidate</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>Once we have invoice prices + Toast sales + 7shifts labor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="44" customHeight="1">
+      <c r="A46" s="7" t="inlineStr"/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Server scorecards (attach rate, turn time)</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Per-server performance.</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Lightspeed Pro, R365, Bbot</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Skip — POS owns it</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>Need POS data only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>Kitchen Ops</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="n"/>
+      <c r="C47" s="26" t="n"/>
+      <c r="D47" s="26" t="n"/>
+      <c r="E47" s="26" t="n"/>
+      <c r="F47" s="26" t="n"/>
+    </row>
+    <row r="48" ht="44" customHeight="1">
+      <c r="A48" s="7" t="inlineStr"/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>KDS (Kitchen Display)</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Tickets on a screen at the line; bump on complete.</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Toast KDS (lead), Fresh KDS, Square KDS</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>Bundled with POS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="44" customHeight="1">
+      <c r="A49" s="9" t="inlineStr"/>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>Recipe / spec display</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Show plating, allergens, recipe at the line.</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>Apicbase, MarketMan (limited)</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>v3 candidate</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>Once recipes are in, we can render at the station.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="44" customHeight="1">
+      <c r="A50" s="7" t="inlineStr"/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Ticket time analytics</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>How long from fire to ready; bottleneck stations.</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Toast KDS, Lightspeed</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>Skip — KDS owns it</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Same data source as KDS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>Food Safety &amp; Compliance</t>
+        </is>
+      </c>
+      <c r="B51" s="26" t="n"/>
+      <c r="C51" s="26" t="n"/>
+      <c r="D51" s="26" t="n"/>
+      <c r="E51" s="26" t="n"/>
+      <c r="F51" s="26" t="n"/>
+    </row>
+    <row r="52" ht="44" customHeight="1">
+      <c r="A52" s="7" t="inlineStr"/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Temperature logs (walk-ins, hot holding)</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Bluetooth probes log temps; auto-report on regulator audit.</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Therma, Cooper-Atkins, Jolt, MonitorYou</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>v3 candidate</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>Strong fit with our walk-in / station model. Worth pilot test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="44" customHeight="1">
+      <c r="A53" s="9" t="inlineStr"/>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>Line checks / opening / closing</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Daily checklist; signed by manager; photo evidence.</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>Jolt, ChefSafe, FoodDocs, Crunchtime Operations</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>v2 candidate</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>Operations-in-a-box layer. Cheap to build, high adoption signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="44" customHeight="1">
+      <c r="A54" s="7" t="inlineStr"/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>HACCP / food safety plans</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Document HACCP CCPs, monitoring, corrective actions.</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>FoodDocs, Jolt, FoodSafetyMonitor</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Specialist software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="44" customHeight="1">
+      <c r="A55" s="9" t="inlineStr"/>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>Training &amp; certifications (ServSafe, allergen, alcohol)</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Track who's certified, when it expires.</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>Schoox, Discotech, Toast Learning, Crunchtime Training</t>
+        </is>
+      </c>
+      <c r="E55" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>HR adjacent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>Payroll &amp; HR</t>
+        </is>
+      </c>
+      <c r="B56" s="26" t="n"/>
+      <c r="C56" s="26" t="n"/>
+      <c r="D56" s="26" t="n"/>
+      <c r="E56" s="26" t="n"/>
+      <c r="F56" s="26" t="n"/>
+    </row>
+    <row r="57" ht="44" customHeight="1">
+      <c r="A57" s="9" t="inlineStr"/>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>Payroll runs (W-2, W-4, tax)</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Run payroll, file federal/state tax, direct deposit.</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>Toast Payroll, ADP, Gusto, R365 Payroll, 7shifts Payroll</t>
+        </is>
+      </c>
+      <c r="E57" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>High-compliance category.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="44" customHeight="1">
+      <c r="A58" s="7" t="inlineStr"/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Onboarding (I-9, EEO, W-4)</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>New hire paperwork digitized.</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Gusto, Rippling, Toast Payroll</t>
+        </is>
+      </c>
+      <c r="E58" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Adjacent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="44" customHeight="1">
+      <c r="A59" s="9" t="inlineStr"/>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>Tip pooling automation</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Calculate tips, post to payroll, comply with FLSA.</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>TipHaus, 7shifts, Toast Payroll</t>
+        </is>
+      </c>
+      <c r="E59" s="17" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>High-risk if wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="25" t="inlineStr">
+        <is>
+          <t>Admin &amp; Security</t>
+        </is>
+      </c>
+      <c r="B60" s="26" t="n"/>
+      <c r="C60" s="26" t="n"/>
+      <c r="D60" s="26" t="n"/>
+      <c r="E60" s="26" t="n"/>
+      <c r="F60" s="26" t="n"/>
+    </row>
+    <row r="61" ht="44" customHeight="1">
+      <c r="A61" s="9" t="inlineStr"/>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>RBAC (counter / manager / admin)</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Role-based access. Counter can't approve their own count.</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>Mise, all enterprise tools</t>
+        </is>
+      </c>
+      <c r="E61" s="17" t="inlineStr">
+        <is>
+          <t>Have</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>RLS on every table. Day-one design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="44" customHeight="1">
+      <c r="A62" s="7" t="inlineStr"/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Audit log on every mutation</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Every state change written to immutable log.</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Mise, R365, Restaurant365 (best of category)</t>
+        </is>
+      </c>
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>Have</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>Changelog UI shipped today. Backed by audit_log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="44" customHeight="1">
+      <c r="A63" s="9" t="inlineStr"/>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>User invites + role assignment</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Invite by email; admin assigns role and locations.</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>All enterprise tools</t>
+        </is>
+      </c>
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>v2 candidate</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>Need before pilot. Supabase Auth + user_restaurants table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="44" customHeight="1">
+      <c r="A64" s="7" t="inlineStr"/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>SSO (Google / Microsoft)</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>Single sign-on; no separate password.</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>R365, Toast (Pro), enterprise</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>v3 candidate</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Once 5+ employee accounts hit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="44" customHeight="1">
+      <c r="A65" s="9" t="inlineStr"/>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>MFA enforcement for admins</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Require 2FA on admin accounts.</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>Most enterprise tools</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>v2 candidate</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>Easy with Supabase Auth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="44" customHeight="1">
+      <c r="A66" s="7" t="inlineStr"/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Data retention + export</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>Indefinite audit log; CSV export for compliance.</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>R365, Toast, MarginEdge</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>Have</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>Retention designed in; export endpoint in Sprint 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="25" t="inlineStr">
+        <is>
+          <t>Integrations &amp; Platform</t>
+        </is>
+      </c>
+      <c r="B67" s="26" t="n"/>
+      <c r="C67" s="26" t="n"/>
+      <c r="D67" s="26" t="n"/>
+      <c r="E67" s="26" t="n"/>
+      <c r="F67" s="26" t="n"/>
+    </row>
+    <row r="68" ht="44" customHeight="1">
+      <c r="A68" s="7" t="inlineStr"/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>POS sales feed (read-only)</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Pull daily sales by item; required for AvT.</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>All inventory tools</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="inlineStr">
+        <is>
+          <t>v2 candidate</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Toast Partner API enrollment. Foundation of v2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="44" customHeight="1">
+      <c r="A69" s="9" t="inlineStr"/>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>Email delivery (transactional)</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>Send invites, alerts, exports.</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>Resend, SendGrid, Postmark</t>
+        </is>
+      </c>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>v2 candidate</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>Resend already in spec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="44" customHeight="1">
+      <c r="A70" s="7" t="inlineStr"/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Slack notifications</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>Post to a kitchen Slack channel on events.</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Most enterprise tools</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>v2 candidate</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>Webhook only — cheap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="44" customHeight="1">
+      <c r="A71" s="9" t="inlineStr"/>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>Webhooks (outbound)</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Push our events to any URL.</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>R365, MarginEdge, enterprise</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>v3 candidate</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>Wait for a customer to ask.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="44" customHeight="1">
+      <c r="A72" s="7" t="inlineStr"/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Public API (read + write)</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>Customers build their own integrations.</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Toast Developer, R365 API, Square API</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>v3 candidate</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>Way later. Internal docs first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="22" t="inlineStr">
+        <is>
+          <t>Verdict legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>Have</t>
+        </is>
+      </c>
+      <c r="B76" s="28" t="inlineStr">
+        <is>
+          <t>Shipped today. Working in the live app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>Building / v2 candidate</t>
+        </is>
+      </c>
+      <c r="B77" s="28" t="inlineStr">
+        <is>
+          <t>Already scoped or scaffolded. Ship as part of v2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>v3 candidate</t>
+        </is>
+      </c>
+      <c r="B78" s="28" t="inlineStr">
+        <is>
+          <t>Worth doing after v2 lands and pilot proves out. 12+ months out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="27" t="inlineStr">
+        <is>
+          <t>Skip — partner</t>
+        </is>
+      </c>
+      <c r="B79" s="28" t="inlineStr">
+        <is>
+          <t>Mature category with a clear winner. Integrate, don't build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
+          <t>Skip — POS owns it</t>
+        </is>
+      </c>
+      <c r="B80" s="28" t="inlineStr">
+        <is>
+          <t>Toast already has the data. Don't replicate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="32" t="inlineStr">
+        <is>
+          <t>Skip — out of scope</t>
+        </is>
+      </c>
+      <c r="B81" s="28" t="inlineStr">
+        <is>
+          <t>Doesn't fit Mise's wedge (counter UX, walk-in, fine dining).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="22" t="inlineStr">
+        <is>
+          <t>The scope question</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="280" customHeight="1">
+      <c r="A85" s="23" t="inlineStr">
+        <is>
+          <t>If Mise truly 'manages everything,' we become Restaurant365 — a 5-year, $50M+ effort with an enterprise sales team. The current pitch is the opposite: 'we don't try to be R365 — we fix the one part R365 / xtraCHEF can't get adoption on.' Both stories are valid. They are not the same product.
+Two clean paths forward:
+1) STAY NARROW — Inventory-first. We build the v2 punch list (Toast sync, OCR, recipes, AvT, below-par alerts, photo + dual count, audit log). Everything else stays partner / integration. Time to v2 in production: 5–7 months. Funded by the xtraCHEF savings.
+2) GO WIDE — 'Gioia ops console.' Mise becomes the single pane of glass: inventory + scheduling (via 7shifts API) + reservations (via SevenRooms API) + accounting handoff (via R365 / QuickBooks) + line-check tasks. We don't build the underlying tools — we own the dashboard that surfaces all of them. 9–12 month roadmap. More positioning lift than build.
+Recommendation: do option 1 cleanly, get the FTL pilot working, then expand to option 2 as a 'we already won inventory; now we surface everything in one place' story. The two paths compound. Trying to start with option 2 means we miss our wedge.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B76:F76"/>
+    <mergeCell ref="B79:F79"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>